--- a/artfynd/A 21628-2026 artfynd.xlsx
+++ b/artfynd/A 21628-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982207</v>
+        <v>74027645</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>107867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Hypochoeris maculata. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Anthemis arvensis. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74027645</v>
+        <v>73982207</v>
       </c>
       <c r="B3" t="n">
-        <v>107338</v>
+        <v>109814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1855</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Anthemis arvensis. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Hypochoeris maculata. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74153255</v>
+        <v>74843784</v>
       </c>
       <c r="B4" t="n">
-        <v>98589</v>
+        <v>106155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,19 +908,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Dactylorhiza maculata ssp. maculata. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Primula veris. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74463399</v>
+        <v>74782298</v>
       </c>
       <c r="B5" t="n">
-        <v>104150</v>
+        <v>102559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,19 +1019,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Helianthemum nummularium ssp. nummularium. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Polygala vulgaris. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74843784</v>
+        <v>74153255</v>
       </c>
       <c r="B6" t="n">
-        <v>105644</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,23 +1130,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Primula veris. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Dactylorhiza maculata ssp. maculata. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,6 +1219,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74463399</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gubbelyckan, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>583807</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6372440</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1995-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1995-07-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G4h 3605. SOM: Helianthemum nummularium ssp. nummularium. LEG: Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Markberedd och granplanterad åker</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 21628-2026 artfynd.xlsx
+++ b/artfynd/A 21628-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74027645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,8 +1360,21 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74463399</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>